--- a/files_by_year/2023_randomsample.xlsx
+++ b/files_by_year/2023_randomsample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,14 +16,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +48,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,96 +429,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:S63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>DOI</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Published Date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Embargo Release</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>File Count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>File 1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>File 2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>File 3</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>File 4</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>File 5</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>File 6</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>File 7</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>File 8</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>File 9</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>File 10</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>File 11</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>File 12</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>File 13</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
@@ -511,12 +532,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hh63sx09m</t>
+          <t>tt44pn943</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.18130/kjnz-p484</t>
+          <t>10.18130/hjka-dv87</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -524,30 +545,32 @@
           <t>2023-05-09</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>DonisBarrera_Felix_Prospectus.pdf</t>
-        </is>
+      <c r="D2" s="2" t="n">
+        <v>45421</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DonisBarrera_Felix_STSResearchPaper.pdf</t>
+          <t>Kittel_Anna_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DonisBarrera_Felix_SociotechnicalSynthesis.pdf</t>
+          <t>Kittel_Anna_STSResearchPaper.pdf</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DonisBarrera_Felix_TechnicalReport.pdf</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Kittel_Anna_SociotechnicalSynthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Kittel_Anna_TechnicalReport.pdf</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -556,50 +579,51 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zc77sr51d</t>
+          <t>x920fz098</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.18130/e027-hy53</t>
+          <t>10.18130/e3qn-dt37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Prospectus_Suh_Jeremy_2023_BS.pdf</t>
-        </is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>STS_Research_Paper_Suh_Jeremy_2023_BS.pdf</t>
+          <t>Dunnington_Patrick_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sociotechnical_Synthesis_Suh_Jeremy_2023_BS.pdf</t>
+          <t>Dunnington_Patrick_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Technical_Report_Suh_Jeremy_2023_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Dunnington_Patrick_SocioTechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Dunnington_Patrick_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -608,50 +632,53 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="n">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>b5644s72j</t>
+          <t>fx719n646</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.18130/p3nf-6244</t>
+          <t>10.18130/5hgh-8t93</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Jerausek_Andrea_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>45238</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jerausek_Andrea_STS Research Paper.pdf</t>
+          <t>Goldberg_Avery_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jerausek_Andrea_Sociotechnical Synthesis.pdf</t>
+          <t>Goldberg_Avery_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Jerausek_Andrea_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Goldberg_Avery_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Goldberg_Avery_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -660,50 +687,51 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>g158bj67k</t>
+          <t>c534fq24r</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.18130/fz3z-2k50</t>
+          <t>10.18130/j7qy-kx80</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Shamaiengar_Pierson_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shamaiengar_Pierson_STS_Research_Paper.pdf</t>
+          <t>Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Shamaiengar_Pierson_Sociotechnical_Synthesis.pdf</t>
+          <t>Prospectus.pdf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Shamaiengar_Pierson_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -712,50 +740,51 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dz010r28q</t>
+          <t>1g05fc740</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.18130/zwg4-1q25</t>
+          <t>10.18130/y88k-sk75</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Varghese_Mia_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Varghese_Mia_STS_Research_Paper.pdf</t>
+          <t>1_Le_Myanh_2023_BS.pdf</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Varghese_Mia_Sociotechnical_Synthesis.pdf</t>
+          <t>2_Le_Myanh_2023_BS.pdf</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Varghese_Mia_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>3_Le_Myanh_2023_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4_Le_Myanh_2023_BS.pdf</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -764,50 +793,51 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="n">
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8c97kr63p</t>
+          <t>zg64tn073</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.18130/yqtv-1j42</t>
+          <t>10.18130/g2bp-8a76</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Portfolio_Cover_and_Preface_Johnson_Stephen_2023_BS.pdf</t>
-        </is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Prospectus_Johnson_Stephen_2023_BS.pdf</t>
+          <t>Paine_Stuart_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sociotechnical_Johnson_Stephen_2023_BS.pdf</t>
+          <t>Paine_Stuart_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Technical_Johnson_Stephen_2023_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Paine_Stuart_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Paine_Stuart_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -816,50 +846,51 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hm50tt01n</t>
+          <t>9306t067v</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.18130/j8vf-et93</t>
+          <t>10.18130/pypg-8a10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>STS_Research_Paper.pdf</t>
-        </is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Socio_Technical_Synthesis.pdf</t>
+          <t>Nguyen_Mackenzie_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Technical_Report.pdf</t>
+          <t>Nguyen_Mackenzie_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Thesis_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Nguyen_Mackenzie_Sociotechnical Synthesis.pdf.pdf</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Nguyen_Mackenzie_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -868,50 +899,51 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="n">
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>707958762</t>
+          <t>g445cf526</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.18130/g6tt-db71</t>
+          <t>10.18130/7fxg-n902</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Deadman_Isabelle_Prospectus.pdf</t>
-        </is>
+          <t>2023-12-17</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deadman_Isabelle_STS Research Paper.pdf</t>
+          <t>1_Wu_Yannie_2023_BS.pdf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Deadman_Isabelle_Sociotechnical Synthesis.pdf</t>
+          <t>2_Wu_Yannie_2023_BS.pdf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Deadman_Isabelle_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>3_Wu_Yannie_2023_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4_Wu_Yannie_2023_BS.pdf</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -920,50 +952,51 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fx719n671</t>
+          <t>dn39x2787</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.18130/80q0-ab07</t>
+          <t>10.18130/0924-v587</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Koehler_Matt_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Koehler_Matt_STS Research Paper.pdf</t>
+          <t>Zhang_Connie_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Koehler_Matt_Sociotechnical Synthesis.pdf</t>
+          <t>Zhang_Connie_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Koehler_Matt_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Zhang_Connie_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Zhang_Connie_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -972,50 +1005,51 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>b2773w932</t>
+          <t>td96k361p</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10.18130/z3tf-g093</t>
+          <t>10.18130/spvf-x073</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Moore_Dylan_Executive Summary.pdf</t>
-        </is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Moore_Dylan_Prospectus.pdf</t>
+          <t>Kremp_Andrew_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moore_Dylan_STS Research Paper.pdf</t>
+          <t>Kremp_Andrew_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Moore_Dylan_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Kremp_Andrew_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Kremp_Andrew_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1024,50 +1058,51 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dr26xz771</t>
+          <t>9w0324248</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.18130/4mmj-gt95</t>
+          <t>10.18130/1j01-ap47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Gross_Tristan_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gross_Tristan_STS_Research_Paper.pdf</t>
+          <t>Gould_Sarah_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gross_Tristan_Sociotechnical_Synthesis.pdf</t>
+          <t>Gould_Sarah_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Gross_Tristan_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Gould_Sarah_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Gould_Sarah_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1076,19 +1111,20 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6969z199c</t>
+          <t>qv33rx821</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10.18130/h3zx-mp83</t>
+          <t>10.18130/zpqb-gm80</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1096,30 +1132,30 @@
           <t>2023-05-12</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1_Phan_Eddy_2023_BS.pdf</t>
-        </is>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2_Phan_Eddy_2023_BS.pdf</t>
+          <t>Williams_Willis_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3_Phan_Eddy_2023_BS.pdf</t>
+          <t>Williams_Willis_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4_Phan_Eddy_2023_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Williams_Willis_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Williams_Willis_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1128,19 +1164,20 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="n">
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>p8418p53b</t>
+          <t>7m01bm78z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10.18130/y46d-yp37</t>
+          <t>10.18130/q86x-cn32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1148,30 +1185,30 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1_McGhee_Noah_SociotechnicalSynthesis.pdf</t>
-        </is>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2_McGhee_Noah_TechnicalReport.pdf</t>
+          <t>Streetman_MaryVictoria_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3_McGhee_Noah_STSResearchPaper.pdf</t>
+          <t>Streetman_MaryVictoria_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4_McGhee_Noah_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Streetman_MaryVictoria_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Streetman_MaryVictoria_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1180,50 +1217,51 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="n">
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3484zj02f</t>
+          <t>2n49t284m</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10.18130/x4bz-rp95</t>
+          <t>10.18130/8yn4-4e54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Whelan_Matthew_STS_RP.pdf</t>
-        </is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Whelan_Matthew_Technical_Report.pdf</t>
+          <t>Saeed_Haris_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Whelan_Matthew_Thesis_Prospectus.pdf</t>
+          <t>Saeed_Haris_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Whelan_Matthew_Title_Sociotechnical_Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Saeed_Haris_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Saeed_Haris_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1232,50 +1270,53 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="n">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rx913r029</t>
+          <t>0z708x823</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.18130/19ky-rm49</t>
+          <t>10.18130/6h2c-yz63</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Patel_Priti_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>45792</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Patel_Priti_STS_Research_Paper.pdf</t>
+          <t>Sander_Molly_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Patel_Priti_Sociotechnical_Synthesis.pdf</t>
+          <t>Sander_Molly_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Patel_Priti_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Sander_Molly_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sander_Molly_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1284,50 +1325,51 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>j38608134</t>
+          <t>73666601f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10.18130/bem4-3v72</t>
+          <t>10.18130/vbzb-t659</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Prospectus_Keaton_Brendan_2023_BS.pdf</t>
-        </is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>STS_Keaton_Brendan_2023_BS.pdf</t>
+          <t>Prospectus_Clements_Lex_2023_BS.pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Synthesis_Keaton_Brendan_2023_BS.pdf</t>
+          <t>STS_Research_Paper_Clements_Lex_2023_BS.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Technical_Keaton_Brendan_2023_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Sociotechnical_Synthesis_Clements_Lex_2023_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Technical_Report_Clements_Lex_2023_BS.pdf</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1336,19 +1378,20 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="n">
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pk02cb94c</t>
+          <t>x059c837w</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10.18130/q46e-8h20</t>
+          <t>10.18130/x7t6-9h51</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1356,30 +1399,30 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1_Nguyen_Jared_2023_BS.pdf</t>
-        </is>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2_Nguyen_Jared_2023_BS.pdf</t>
+          <t>Cresci_Alexandra_2023_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3_Nguyen_Jared_2023_BS.pdf</t>
+          <t>Cresci_Alexandra_2023_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4_Nguyen_Jared_2023_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Cresci_Alexandra_2023_STS.pdf</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Cresci_Alexandra_2023_Technical.pdf</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1388,19 +1431,20 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="n">
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>vq27zp69c</t>
+          <t>m039k601m</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10.18130/660a-zy93</t>
+          <t>10.18130/07qj-en92</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1408,30 +1452,30 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Rampa_Pulkit_Executive Summary.pdf</t>
-        </is>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rampa_Pulkit_Prospectus.pdf</t>
+          <t>Suliman_Dio_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rampa_Pulkit_STSResearch Paper.pdf</t>
+          <t>Suliman_Dio_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Rampa_Pulkit_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Suliman_Dio_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Suliman_Dio_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1440,52 +1484,49 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="n">
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>xd07gt933</t>
+          <t>4x51hk17x</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10.18130/6p4y-5f98</t>
+          <t>10.18130/x4md-fc26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>5</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Cover Page</t>
-        </is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Preface</t>
+          <t>Haddad_Nicholas_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Prospectus</t>
+          <t>Haddad_Nicholas_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sociotechnical Research Paper</t>
+          <t>Haddad_Nicholas_Sociotechnical Synthesis.pdf</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Technical Report</t>
+          <t>Haddad_Nicholas_Technical Report.pdf</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1496,50 +1537,51 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="n">
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>zk51vh95r</t>
+          <t>j6731502v</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10.18130/qxs8-b070</t>
+          <t>10.18130/hq6f-qk71</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Gonzalez_Nathaniel_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gonzalez_Nathaniel_STS Research Paper.pdf</t>
+          <t>Connors_James_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gonzalez_Nathaniel_Sociotechnical Synthesis.pdf</t>
+          <t>Connors_James_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Gonzalez_Nathaniel_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Connors_James_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Connors_James_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1548,19 +1590,20 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="n">
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gx41mj95v</t>
+          <t>h989r4587</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10.18130/hgkh-k822</t>
+          <t>10.18130/7hep-2520</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1568,30 +1611,30 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Crisanto_Alvaro_Prospectus.pdf</t>
-        </is>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Crisanto_Alvaro_STS Research Paper.pdf</t>
+          <t>Flici_Brant_Executive_Summary.pdf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crisanto_Alvaro_Sociotechnical Synthesis.pdf</t>
+          <t>Flici_Brant_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Crisanto_Alvaro_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Flici_Brant_STS_Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Flici_Brant_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1600,50 +1643,53 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="n">
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>g158bj651</t>
+          <t>zw12z673q</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10.18130/zh8j-nq65</t>
+          <t>10.18130/7vft-2m74</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Jones_Sean_Executive_Summary.pdf</t>
-        </is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>45240</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jones_Sean_Prospectus.pdf</t>
+          <t>1_Goldman_Drew_2023_BS.pdf</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Jones_Sean_STS_Research_Paper.pdf</t>
+          <t>2_Goldman_Drew_2023_BS.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Jones_Sean_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>3_Goldman_Drew_2023_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4_Goldman_Drew_2023_BS.pdf</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1652,50 +1698,51 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="n">
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cv43nz02j</t>
+          <t>8910jv78t</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10.18130/y7y8-ks32</t>
+          <t>10.18130/dfg7-0b88</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Bergloff_Bjorn_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bergloff_Bjorn_STS Research Paper.pdf</t>
+          <t>Richwine_Michael_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bergloff_Bjorn_Sociotechnical Synthesis.pdf</t>
+          <t>Richwine_Michael_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bergloff_Bjorn_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Richwine_Michael_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Richwine_Michael_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1704,50 +1751,53 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>js956g99b</t>
+          <t>dz010r354</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10.18130/f2tk-n245</t>
+          <t>10.18130/xmdb-ek50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>4</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Haslet-Executive_Summary.pdf</t>
-        </is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>45291</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Haslet-Prospectus.pdf</t>
+          <t>Bhargava_Sarah_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Haslet-STS_Research_Paper.pdf</t>
+          <t>Bhargava_Sarah_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Haslet-Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Bhargava_Sarah_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Bhargava_Sarah_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1756,50 +1806,51 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="n">
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ht24wk55h</t>
+          <t>707958762</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10.18130/b46a-5838</t>
+          <t>10.18130/g6tt-db71</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>1_Pham_Selena_Sociotechnical_Synthesis.pdf</t>
-        </is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2_Pham_Selena_Technical_Report.pdf</t>
+          <t>Deadman_Isabelle_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3_Pham_Selena_STS_Reseach_Paper.pdf</t>
+          <t>Deadman_Isabelle_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4_Pham_Selena_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Deadman_Isabelle_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Deadman_Isabelle_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1808,50 +1859,51 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="n">
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fj2363366</t>
+          <t>st74cr86r</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10.18130/r35y-2353</t>
+          <t>10.18130/4evt-ym93</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Shamsie_Taha_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shamsie_Taha_STS Research Paper.pdf</t>
+          <t>Brinkley_Bill_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Shamsie_Taha_Sociotechnical Synthesis.pdf</t>
+          <t>Brinkley_William_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Shamsie_Taha_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Brinkley_William_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Brinkley_William_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1860,19 +1912,20 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="n">
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9w0324248</t>
+          <t>8910jv814</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10.18130/1j01-ap47</t>
+          <t>10.18130/33xj-c470</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1880,30 +1933,30 @@
           <t>2023-05-12</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Gould_Sarah_Prospectus.pdf</t>
-        </is>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gould_Sarah_STS Research Paper.pdf</t>
+          <t>Poley_Alexander_Executive_Summary.pdf</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gould_Sarah_Sociotechnical Synthesis.pdf</t>
+          <t>Poley_Alexander_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Gould_Sarah_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Poley_Alexander_STS_Research_Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Poley_Alexander_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -1912,50 +1965,51 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="n">
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2801ph476</t>
+          <t>hh63sx09m</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10.18130/gc0r-pp23</t>
+          <t>10.18130/kjnz-p484</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>McElhinney_Eamon_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>4</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>McElhinney_Eamon_STS Research Paper.pdf</t>
+          <t>DonisBarrera_Felix_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>McElhinney_Eamon_Sociotechnical Synthesis.pdf</t>
+          <t>DonisBarrera_Felix_STSResearchPaper.pdf</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>McElhinney_Eamon_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>DonisBarrera_Felix_SociotechnicalSynthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>DonisBarrera_Felix_TechnicalReport.pdf</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -1964,50 +2018,51 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>nc580n904</t>
+          <t>rv042v155</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10.18130/m9p5-pj14</t>
+          <t>10.18130/z4xf-9h82</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Sohail_Moeez_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sohail_Moeez_STS Research Paper.pdf</t>
+          <t>Steele_Ryan_Preface.pdf</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sohail_Moeez_Sociotechnical Synthesis.pdf</t>
+          <t>Steele_Ryan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sohail_Moeez_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Steele_Ryan_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Steele_Ryan_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2016,50 +2071,51 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="n">
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>m039k601m</t>
+          <t>vm40xs793</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10.18130/07qj-en92</t>
+          <t>10.18130/wde7-mm02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Suliman_Dio_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Suliman_Dio_STS Research Paper.pdf</t>
+          <t>Casco_Nicole_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Suliman_Dio_Sociotechnical Synthesis.pdf</t>
+          <t>Casco_Nicole_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Suliman_Dio_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Casco_Nicole_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Casco_Nicole_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2068,19 +2124,20 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="n">
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4t64gp40g</t>
+          <t>ms35t983z</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10.18130/6fqf-7s63</t>
+          <t>10.18130/4b04-ms94</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2088,30 +2145,32 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Parson_Alex_Prospectus.pdf</t>
-        </is>
+      <c r="D32" s="2" t="n">
+        <v>45423</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Parson_Alex_STS_Research_Paper.pdf</t>
+          <t>Mirt_Jared_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parson_Alex_Sociotechnical_Synthesis.pdf</t>
+          <t>Mirt_Jared_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Parson_Alex_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Mirt_Jared_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Mirt_Jared_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2120,19 +2179,20 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="n">
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>td96k361p</t>
+          <t>3n2040298</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10.18130/spvf-x073</t>
+          <t>10.18130/rp8q-ch05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2140,30 +2200,30 @@
           <t>2023-05-09</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Kremp_Andrew_Prospectus.pdf</t>
-        </is>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>4</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kremp_Andrew_STS_Research_Paper.pdf</t>
+          <t>Hasani_David_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Kremp_Andrew_Sociotechnical_Synthesis.pdf</t>
+          <t>Hasani_David_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kremp_Andrew_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Hasani_David_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Hasani_David_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2172,19 +2232,20 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="n">
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5138jf94c</t>
+          <t>hd76s116z</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10.18130/be92-ad45</t>
+          <t>10.18130/mwce-kj96</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2192,30 +2253,30 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Prospectus_Javaid_Rehan_2023_BSCS.pdf</t>
-        </is>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>STS_Thesis_Javaid_Rehan_2023_BSCS.pdf</t>
+          <t>Barbosa_Collin_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sociotechnical_Synthesis_Javaid_Rehan_2023_BSCS.pdf</t>
+          <t>Barbosa_Collin_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Technical_Report_Javaid_Rehan_2023_BSCS.pdf</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Barbosa_Collin_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Barbosa_Collin_Technical_ReportV2.pdf</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2224,50 +2285,53 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="n">
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>44558f558</t>
+          <t>sj139314x</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10.18130/g4k7-4p49</t>
+          <t>10.18130/e234-rk15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1_Li_Alan_2023_BS.pdf</t>
-        </is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>45240</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2_Li_Alan_2023_BS.pdf</t>
+          <t>Spinelli_Van_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3_Li_Alan_2023_BS.pdf</t>
+          <t>Spinelli_Van_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4_Li_Alan_2023_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Spinelli_Van_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Spinelli_Van_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2276,51 +2340,56 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="n">
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>h415pb91j</t>
+          <t>1z40kt920</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10.18130/1y9z-4c40</t>
+          <t>10.18130/q2w4-cq37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Pham_Khoi_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pham_Khoi_STS_Research_Paper.pdf</t>
+          <t>Jiang_Qinyuan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pham_Khoi_Sociotechnical_Synthesis.pdf</t>
+          <t>Jiang_Qinyuan_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pham_Khoi_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>Jiang_Qinyuan_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Jiang_Qinyuan_Technical Report CS.pdf</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Jiang_Qinyuan_Technical Report Systems.pdf</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -2328,50 +2397,51 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="n">
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9593tw25c</t>
+          <t>j9602195w</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10.18130/awkq-8842</t>
+          <t>10.18130/x3y5-pj26</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Joachim_Julia_Prospectus.pdf</t>
-        </is>
+          <t>2023-12-17</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Joachim_Julia_STS Research Paper.pdf</t>
+          <t>Capstone_Asthana_Raj_2023_BS.pdf</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Joachim_Julia_Sociotechnical Synthesis.pdf</t>
+          <t>Prospectus_Asthana_Raj_2023_BS.pdf</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Joachim_Julia_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>STSRP_Asthana_Raj_2023_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Synthesis_Asthana_Raj_2023_BS.pdf</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2380,50 +2450,51 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="n">
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8c97kr64z</t>
+          <t>3r074w29m</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10.18130/2cn0-hr03</t>
+          <t>10.18130/py75-ds69</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Hamby_John_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hamby_John_STS Research Paper.pdf</t>
+          <t>4_Hunter_Kyle_2023_BS.pdf</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hamby_John_Sociotechnical Synthesis.pdf</t>
+          <t>Hunter_Kyle_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Hamby_John_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Hunter_Kyle_STS_Research_Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Hunter_Kyle_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -2432,19 +2503,20 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="n">
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>k0698869d</t>
+          <t>dr26xz76r</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10.18130/j7sc-0h17</t>
+          <t>10.18130/p5e0-xz56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2452,30 +2524,30 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Nguyen_Andrew_Prospectus.pdf</t>
-        </is>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nguyen_Andrew_STS Research Paper.pdf</t>
+          <t>Baggs_Emil_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nguyen_Andrew_Sociotechnical Synthesis.pdf</t>
+          <t>Baggs_Emil_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Nguyen_Andrew_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Baggs_Emil_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Baggs_Emil_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -2484,19 +2556,20 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="n">
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>9p290b57b</t>
+          <t>2r36tz81v</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10.18130/5zc1-f265</t>
+          <t>10.18130/8513-t329</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2504,30 +2577,30 @@
           <t>2023-05-11</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Corona_Madeline_Prospectus.pdf</t>
-        </is>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Corona_Madeline_STS Research Paper.pdf</t>
+          <t>Keller_Ryan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Corona_Madeline_Sociotechnical Synthesis.pdf</t>
+          <t>Keller_Ryan_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Corona_Madeline_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Keller_Ryan_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Keller_Ryan_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2536,51 +2609,56 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4t64gp375</t>
+          <t>6h440t61w</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10.18130/zryq-g478</t>
+          <t>10.18130/1s2b-0k57</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Grace_Cooper_Executive Summary.pdf</t>
-        </is>
+          <t>2023-05-05</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grace_Cooper_Prospectus.pdf</t>
+          <t>Himley_Aidan_Executive_Summary.pdf</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Grace_Cooper_STS Research Paper.pdf</t>
+          <t>Himley_Aidan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Grace_Cooper_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>Himley_Aidan_STS_Research_Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Himley_Aidan_Technical_Report_CS.pdf</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Himley_Aidan_Technical_Report_CpE.pdf</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
@@ -2588,50 +2666,51 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="n">
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9w032422q</t>
+          <t>wm117q16t</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10.18130/14wp-et50</t>
+          <t>10.18130/k2qq-g230</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2023-05-08</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>William_McCollough_Cover_Page_Preface.pdf</t>
-        </is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>William_McCollough_Prospectus.pdf</t>
+          <t>Ardura_George_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>William_McCollough_Sociotechnical_Research_Paper_2023.pdf</t>
+          <t>Ardura_George_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>William_McCollough_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Ardura_George_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Ardura_George_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -2640,50 +2719,51 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="n">
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2z10wr43x</t>
+          <t>mc87pr48b</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10.18130/b8nz-4404</t>
+          <t>10.18130/31ft-d589</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Llewellyn_Asher_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Llewellyn_Asher_STS Research Paper.pdf</t>
+          <t>Huang_James_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Llewellyn_Asher_Sociotechnical Synthesis.pdf</t>
+          <t>Huang_James_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Llewellyn_Asher_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Huang_James_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Huang_James_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2692,19 +2772,20 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="n">
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>gt54kp24v</t>
+          <t>0c483k68z</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10.18130/g6c3-5641</t>
+          <t>10.18130/5e6n-z127</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2712,30 +2793,30 @@
           <t>2023-05-09</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Sanchez_Ansel_Prospectus.pdf</t>
-        </is>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sanchez_Ansel_STS_Research_Paper.pdf</t>
+          <t>Le_Teagan_Capstone_Report.pdf</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sanchez_Ansel_Sociotechnical_Synthesis.pdf</t>
+          <t>Le_Teagan_Cover_Page.pdf</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sanchez_Ansel_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Le_Teagan_Prospectus.pdf</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Le_Teagan_STS_Research_Paper.pdf</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2744,19 +2825,20 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="n">
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sx61dn614</t>
+          <t>db78td244</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10.18130/4w55-nm09</t>
+          <t>10.18130/brz6-h160</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2764,30 +2846,30 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>1_Barnes_Kevin_2023_BS.pdf</t>
-        </is>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2_Barnes_Kevin_2023_BS.pdf</t>
+          <t>Myott_Madison_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3_Barnes_Kevin_2023_BS.pdf</t>
+          <t>Myott_Madison_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>4_Barnes_Kevin_2023_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>Myott_Madison_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Myott_Madison_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -2796,50 +2878,51 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="n">
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>x346d551z</t>
+          <t>dv13zv272</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10.18130/3x77-6x18</t>
+          <t>10.18130/hqmh-ey73</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Bilali_Dani_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-13</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bilali_Dani_STS Research Paper.pdf</t>
+          <t>Bouzar_Nathan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bilali_Dani_Sociotechnical Synthesis.pdf</t>
+          <t>Bouzar_Nathan_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Bilali_Dani_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Bouzar_Nathan_Socio_technical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Bouzar_Nathan_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -2848,50 +2931,53 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="n">
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tt44pn95c</t>
+          <t>rf55z867q</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10.18130/z3yg-ae02</t>
+          <t>10.18130/t1q0-5n62</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Sharma_Nikhil_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>45240</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sharma_Nikhil_STS Research Paper.pdf</t>
+          <t>Burnside_Alex_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sharma_Nikhil_Sociotechnical Synthesis.pdf</t>
+          <t>Burnside_Alex_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sharma_Nikhil_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Burnside_Alex_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Burnside_Alex_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -2900,50 +2986,51 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="n">
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>xp68kh355</t>
+          <t>7m01bm94b</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10.18130/2ggh-5362</t>
+          <t>10.18130/hk49-8m19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Ritchie_Emma_Prospectus.pdf</t>
-        </is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ritchie_Emma_STS Research Paper.pdf</t>
+          <t>Yoon_Claire_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ritchie_Emma_Sociotechnical Synthesis.pdf</t>
+          <t>Yoon_Claire_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Ritchie_Emma_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Yoon_Claire_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Yoon_Claire_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -2952,50 +3039,51 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="n">
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>rb68xd344</t>
+          <t>qv33rx78f</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10.18130/8zry-6b71</t>
+          <t>10.18130/mshc-fv34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2023-12-16</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Panagides_Anthony_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-06</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Panagides_Anthony_STS_Research_Paper.pdf</t>
+          <t>Bannon_Joseph_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Panagides_Anthony_Sociotechnical_Synthesis.pdf</t>
+          <t>Bannon_Joseph_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Panagides_Anthony_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>Bannon_Joseph_Technical_Report.pdf</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Bannon_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -3004,50 +3092,51 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="n">
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3484zj00w</t>
+          <t>9p290b57b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10.18130/s56k-f620</t>
+          <t>10.18130/5zc1-f265</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Chittari_Srikar_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chittari_Srikar_STS Research Paper.pdf</t>
+          <t>Corona_Madeline_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chittari_Srikar_Sociotechnical Synthesis.pdf</t>
+          <t>Corona_Madeline_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Chittari_Srikar_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Corona_Madeline_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Corona_Madeline_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -3056,50 +3145,53 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="n">
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pc289k44w</t>
+          <t>b5644s75c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10.18130/e4h3-nh27</t>
+          <t>10.18130/k4wj-tc84</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Chadha_Samir_Executive Summary.pdf</t>
-        </is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>45787</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chadha_Samir_Prospectus.pdf</t>
+          <t>1_Zhao_Daniel_2023_BS.pdf</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chadha_Samir_STS Research Paper.pdf</t>
+          <t>2_Zhao_Daniel_2023_BS.pdf</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Chadha_Samir_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>3_Zhao_Daniel_2023_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4_Zhao_Daniel_2023_BS.pdf</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -3108,50 +3200,51 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="n">
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>c534fq23g</t>
+          <t>5x21tg93d</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10.18130/hx7r-rv88</t>
+          <t>10.18130/2qpg-as70</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Gray - Executive Summary.pdf</t>
-        </is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>4</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gray - Prospectus.pdf</t>
+          <t>Jayaraman_Anupama_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gray - STS Research Paper.pdf</t>
+          <t>Jayaraman_Anupama_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Gray - Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Jayaraman_Anupama_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Jayaraman_Anupama_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3160,50 +3253,51 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="n">
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3r074w29m</t>
+          <t>pk02cb94c</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10.18130/py75-ds69</t>
+          <t>10.18130/q46e-8h20</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>4_Hunter_Kyle_2023_BS.pdf</t>
-        </is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>4</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hunter_Kyle_Prospectus.pdf</t>
+          <t>1_Nguyen_Jared_2023_BS.pdf</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hunter_Kyle_STS_Research_Paper.pdf</t>
+          <t>2_Nguyen_Jared_2023_BS.pdf</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Hunter_Kyle_Sociotechnical_Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>3_Nguyen_Jared_2023_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4_Nguyen_Jared_2023_BS.pdf</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3212,50 +3306,51 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="n">
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>qr46r201z</t>
+          <t>j3860801b</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10.18130/tq8f-fv07</t>
+          <t>10.18130/wjfj-by85</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Wang_Cynthia_Executive_Summary.pdf</t>
-        </is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wang_Cynthia_Prospectus.pdf</t>
+          <t>Taylor_Jacob_Executive_Summary.pdf</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Wang_Cynthia_STS_Research_Paper.pdf</t>
+          <t>Taylor_Jacob_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Wang_Cynthia_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Taylor_Jacob_STS_Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Taylor_Jacob_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3264,50 +3359,51 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="n">
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0c483k75c</t>
+          <t>ft848r69b</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10.18130/xdy0-7m53</t>
+          <t>10.18130/dshj-jw87</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Lee_Joseph_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-13</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>4</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lee_Joseph_Research Paper.pdf</t>
+          <t>Galletta_Sam_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lee_Joseph_Sociotechnical Synthesis.pdf</t>
+          <t>Galletta_Sam_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Lee_Joseph_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Galletta_Sam_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Galletta_Sam_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3316,50 +3412,51 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="n">
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2n49t279r</t>
+          <t>z890rv479</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10.18130/gvsd-dc93</t>
+          <t>10.18130/8dtz-mz04</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Dugan_Thomas_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-05</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>4</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dugan_Thomas_STS Research Paper.pdf</t>
+          <t>Lower-Basch_Daniel_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dugan_Thomas_Sociotechnical Synthesis.pdf</t>
+          <t>Lower-Basch_Daniel_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Dugan_Thomas_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Lower-Basch_Daniel_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Lower-Basch_Daniel_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -3368,50 +3465,53 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="n">
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>xk81jm511</t>
+          <t>qb98mg69c</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10.18130/te10-yz90</t>
+          <t>10.18130/y9yx-bp87</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Gahm_Ethan_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>45424</v>
+      </c>
+      <c r="E57" t="n">
+        <v>4</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gahm_Ethan_STS_Research_Paper.pdf</t>
+          <t>Stauffer_Peter_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gahm_Ethan_Sociotechnical_Synthesis.pdf</t>
+          <t>Stauffer_Peter_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Gahm_Ethan_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Stauffer_Peter_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Stauffer_Peter_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -3420,19 +3520,20 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="n">
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>s7526d619</t>
+          <t>wp988m151</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10.18130/qvv3-b733</t>
+          <t>10.18130/yamc-zm78</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3440,30 +3541,30 @@
           <t>2023-05-12</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Sawyer_Allison_Prospectus.pdf</t>
-        </is>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sawyer_Allison_STS Research Paper.pdf</t>
+          <t>1_Sam_Joseph_2023_BS.pdf</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sawyer_Allison_Sociotechnical Synthesis.pdf</t>
+          <t>2_Sam_Joseph_2023_BS.pdf</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sawyer_Allison_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>3_Sam_Joseph_2023_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>4_Sam_Joseph_2023_BS.pdf</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -3472,50 +3573,51 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="n">
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>g732db052</t>
+          <t>5x21tg860</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10.18130/pztn-b595</t>
+          <t>10.18130/trdy-q537</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>1_OMalley_Malcolm_2023_BS.pdf</t>
-        </is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>4</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2_OMalley_Malcolm_2023_BS.pdf</t>
+          <t>3_Erhabor_Emmanuel_Sociotechnical_Synthesis.pdf</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3_OMalley_Malcolm_2023_BS.pdf</t>
+          <t>Erhabor_Emmanuel_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4_OMalley_Malcolm_2023_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Erhabor_Emmanuel_STS_Research_Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Erhabor_Emmanuel_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
@@ -3524,19 +3626,20 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="n">
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>qb98mg73z</t>
+          <t>cj82k855r</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10.18130/g76r-7p34</t>
+          <t>10.18130/qmh0-x726</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3544,30 +3647,30 @@
           <t>2023-05-10</t>
         </is>
       </c>
-      <c r="D60" t="n">
-        <v>4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Edwards_Ailene_ExecutiveSummary.pdf</t>
-        </is>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>4</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Edwards_Ailene_Prospectus.pdf</t>
+          <t>Liu-Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Edwards_Ailene_STSResearchPaper.pdf</t>
+          <t>Liu-Prospectus.pdf</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Edwards_Ailene_TechnicalReport.pdf</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>Liu-STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Liu-Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -3576,50 +3679,51 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="n">
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>v118rg07r</t>
+          <t>sf268624x</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10.18130/je0g-n875</t>
+          <t>10.18130/z67q-ng02</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Zheng_Alan_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-08</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>4</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Zheng_Alan_STS_Paper.pdf</t>
+          <t>Miller_Carole_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Zheng_Alan_Sociotechnical_Synthesis.pdf</t>
+          <t>Miller_Carole_STSResearchPaper.pdf</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Zheng_Alan_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Miller_Carole_SociotechnicalSynthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Miller_Carole_TechnicalReport.pdf</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
@@ -3628,50 +3732,51 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>12579t46s</t>
+          <t>3b5919733</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10.18130/h33c-0q41</t>
+          <t>10.18130/tfph-yn34</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Ashbahian_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-09</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>4</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ashbahian_ResearchPaper.pdf</t>
+          <t>Mcilyar_Marshall_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ashbahian_SociotechnicalSynthesis.pdf</t>
+          <t>Mcilyar_Marshall_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Ashbahian_TechnicalReport.pdf</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Mcilyar_Marshall_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Mcilyar_Marshall_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
@@ -3680,50 +3785,51 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="n">
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="n">
         <v>2023</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>8g84mn71m</t>
+          <t>q524jp97t</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>10.18130/t90w-ry49</t>
+          <t>10.18130/m9hr-gv28</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Bonner_Brandon_Prospectus.pdf</t>
-        </is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>4</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bonner_Brandon_STS Research Paper.pdf</t>
+          <t>Mbogo_Brian_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bonner_Brandon_Sociotechnical Synthesis.pdf</t>
+          <t>Mbogo_Brian_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bonner_Brandon_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>Mbogo_Brian_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Mbogo_Brian_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
@@ -3732,371 +3838,8 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="n">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>q524jp97t</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>10.18130/m9hr-gv28</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Mbogo_Brian_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Mbogo_Brian_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Mbogo_Brian_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Mbogo_Brian_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="n">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>3484zj015</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>10.18130/9kbj-0p41</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>1_Forkin_Ekaterina_2023_BS.pdf</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2_Forkin_Ekaterina_2023_BS.pdf</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>3_Forkin_Ekaterina_2023_BS.pdf</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>4_Forkin_Ekaterina_2023_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="n">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>n583xw37x</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>10.18130/c2v0-6q74</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Cuomo_Alexa_Executive Summary.pdf</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Cuomo_Alexa_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Cuomo_Alexa_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Cuomo_Alexa_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="n">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>sx61dn64z</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>10.18130/qqhx-tw58</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2023-05-09</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Illoh_Chioma_Executive Summary.pdf</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Illoh_Chioma_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Illoh_Chioma_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Illoh_Chioma_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="n">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>8910jv84z</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>10.18130/64rv-z313</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Gajjala_Ruthvik_Executive Summary.pdf</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Gajjala_Ruthvik_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Gajjala_Ruthvik_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Gajjala_Ruthvik_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="n">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2b88qd497</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>10.18130/9hh8-dm03</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2023-05-13</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Belisle_Joshua_ExecutiveSummary.pdf</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Belisle_Joshua_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Belisle_Joshua_STSResearchPaper.pdf</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Belisle_Joshua_TechnicalReport.pdf</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="n">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>4x51hk22s</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>10.18130/2dx1-sv60</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Murphy_Lauren_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Murphy_Lauren_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Murphy_Lauren_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Murphy_Lauren_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="n">
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="n">
         <v>2023</v>
       </c>
     </row>
